--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16665" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="24225" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -23,13 +23,13 @@
     <t>type</t>
   </si>
   <si>
-    <t>condtion1</t>
-  </si>
-  <si>
-    <t>condtion2</t>
-  </si>
-  <si>
-    <t>condtion3</t>
+    <t>condition1</t>
+  </si>
+  <si>
+    <t>condition2</t>
+  </si>
+  <si>
+    <t>condition3</t>
   </si>
   <si>
     <t>amount_type</t>
@@ -59,6 +59,9 @@
     <t>[1]</t>
   </si>
   <si>
+    <t>[]</t>
+  </si>
+  <si>
     <t>[2]</t>
   </si>
   <si>
@@ -87,9 +90,6 @@
   </si>
   <si>
     <t>[1,6,3,8]</t>
-  </si>
-  <si>
-    <t>[]</t>
   </si>
 </sst>
 </file>
@@ -112,14 +112,122 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -134,122 +242,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,67 +264,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -336,115 +444,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,11 +460,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,9 +547,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,10 +563,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -575,133 +575,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1105,9 +1105,15 @@
       <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4">
         <v>1</v>
       </c>
@@ -1123,11 +1129,17 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5">
         <v>1</v>
       </c>
@@ -1143,7 +1155,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1160,7 +1181,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1179,9 +1209,15 @@
       <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
       <c r="G8">
         <v>2</v>
       </c>
@@ -1197,11 +1233,17 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
       <c r="G9">
         <v>2</v>
       </c>
@@ -1217,7 +1259,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1234,7 +1285,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1247,6 +1307,24 @@
       <c r="A12">
         <v>9</v>
       </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
       <c r="H12">
         <v>0</v>
       </c>
@@ -1255,6 +1333,24 @@
       <c r="A13">
         <v>10</v>
       </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
       <c r="H13">
         <v>0</v>
       </c>
@@ -1263,6 +1359,24 @@
       <c r="A14">
         <v>11</v>
       </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
       <c r="H14">
         <v>0</v>
       </c>
@@ -1271,6 +1385,24 @@
       <c r="A15">
         <v>12</v>
       </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
       <c r="H15">
         <v>0</v>
       </c>
@@ -1279,6 +1411,24 @@
       <c r="A16">
         <v>13</v>
       </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
       <c r="H16">
         <v>0</v>
       </c>
@@ -1286,6 +1436,24 @@
     <row r="17" spans="1:8">
       <c r="A17">
         <v>14</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1301,9 +1469,15 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
       <c r="G18">
         <v>1</v>
       </c>
@@ -1319,11 +1493,17 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
       <c r="G19">
         <v>1</v>
       </c>
@@ -1339,7 +1519,16 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1356,7 +1545,16 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1373,7 +1571,16 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1390,7 +1597,16 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1407,7 +1623,16 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1427,10 +1652,13 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1447,13 +1675,16 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -1470,7 +1701,16 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1482,6 +1722,21 @@
     <row r="28" spans="1:8">
       <c r="A28">
         <v>25</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1507,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1523,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1531,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1539,7 +1794,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24225" windowHeight="12540"/>
+    <workbookView windowWidth="14280" windowHeight="8850"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -47,7 +47,7 @@
     <t>repeated</t>
   </si>
   <si>
-    <t>1杀怪2对话npc3完成相应条件4使用类型物品5条件池6升级</t>
+    <t>1杀怪2对话npc3完成相应条件4使用类型物品5条件池6升级7不是表里的条件</t>
   </si>
   <si>
     <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)</t>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>condition_id</t>
+  </si>
+  <si>
+    <t>condtion_order</t>
+  </si>
+  <si>
+    <t>0并行1顺序</t>
   </si>
   <si>
     <t>[1,6,3,8]</t>
@@ -97,9 +103,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -126,7 +132,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -134,6 +140,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -211,6 +224,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -225,7 +246,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -240,20 +260,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -264,31 +270,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -300,49 +414,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -354,97 +444,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -455,15 +461,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -547,6 +544,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -566,7 +572,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -575,36 +581,33 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -614,94 +617,97 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1029,7 +1035,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1742,6 +1748,32 @@
         <v>1</v>
       </c>
       <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
         <v>0</v>
       </c>
     </row>
@@ -1754,46 +1786,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="13.875" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>14</v>
       </c>
     </row>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14280" windowHeight="8850"/>
+    <workbookView windowWidth="24225" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -47,7 +47,7 @@
     <t>repeated</t>
   </si>
   <si>
-    <t>1杀怪2对话npc3完成相应条件4使用类型物品5条件池6升级7不是表里的条件</t>
+    <t>1杀怪2对话npc3完成相应条件4使用类型物品5条件池6升级7不是表里的条件8完成相应任务</t>
   </si>
   <si>
     <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)</t>
@@ -103,9 +103,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -117,6 +117,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -126,34 +157,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -167,9 +170,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -191,10 +216,18 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -207,22 +240,13 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -230,32 +254,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,43 +270,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,73 +414,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -396,19 +432,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,37 +444,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,50 +479,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -544,15 +505,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -561,6 +513,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -569,10 +569,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,133 +581,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1035,7 +1035,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1774,6 +1774,32 @@
         <v>1</v>
       </c>
       <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
         <v>0</v>
       </c>
     </row>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24225" windowHeight="12540"/>
+    <workbookView windowWidth="14280" windowHeight="8850" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
     <t>condition_id</t>
   </si>
   <si>
-    <t>condtion_order</t>
+    <t>condition_order</t>
   </si>
   <si>
     <t>0并行1顺序</t>
@@ -103,10 +103,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -114,6 +114,34 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -126,7 +154,54 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -140,38 +215,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,13 +239,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,50 +247,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -253,13 +260,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -270,12 +270,144 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -288,169 +420,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,11 +479,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -517,45 +556,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -569,10 +569,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,16 +581,16 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -599,115 +599,115 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1868,12 +1868,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14280" windowHeight="8850" activeTab="1"/>
+    <workbookView windowWidth="14280" windowHeight="9960" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -89,6 +89,9 @@
     <t>condition_id</t>
   </si>
   <si>
+    <t>random_condition_pool</t>
+  </si>
+  <si>
     <t>condition_order</t>
   </si>
   <si>
@@ -96,6 +99,9 @@
   </si>
   <si>
     <t>[1,6,3,8]</t>
+  </si>
+  <si>
+    <t>[1,2,3,4,5,6,7,8,9,10]</t>
   </si>
 </sst>
 </file>
@@ -103,10 +109,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -118,21 +124,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -147,7 +161,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -178,6 +192,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -199,14 +221,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -223,6 +237,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -231,29 +252,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -270,31 +276,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -306,151 +456,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -461,6 +467,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -479,6 +494,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -490,6 +520,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -526,41 +567,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -569,10 +575,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,133 +587,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1812,14 +1818,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="2" max="3" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1829,8 +1835,11 @@
       <c r="C1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1838,45 +1847,85 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="3:3">
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+    <row r="3" spans="4:4">
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6">
-        <v>1</v>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14280" windowHeight="9960" activeTab="1"/>
+    <workbookView windowWidth="24225" windowHeight="12540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -14,8 +14,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>luhailong</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1:主线</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>1:主线1</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -90,6 +124,12 @@
   </si>
   <si>
     <t>random_condition_pool</t>
+  </si>
+  <si>
+    <t>mission_type</t>
+  </si>
+  <si>
+    <t>mission_sub_type</t>
   </si>
   <si>
     <t>condition_order</t>
@@ -109,17 +149,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -131,7 +178,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -146,13 +193,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -161,7 +201,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,14 +225,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,16 +269,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,11 +286,31 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -276,187 +321,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,16 +539,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -526,17 +571,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -553,17 +587,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -575,10 +620,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -587,133 +632,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1818,14 +1863,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="2" max="3" width="20.25" customWidth="1"/>
+    <col min="2" max="5" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1838,8 +1883,14 @@
       <c r="D1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1852,13 +1903,19 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="4:4">
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="6:6">
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1869,15 +1926,21 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>14</v>
@@ -1885,8 +1948,14 @@
       <c r="D5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1894,13 +1963,19 @@
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1908,13 +1983,19 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1922,14 +2003,21 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24225" windowHeight="12540" activeTab="1"/>
+    <workbookView windowWidth="16575" windowHeight="10545" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -49,12 +49,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>type</t>
+    <t>condition_type</t>
   </si>
   <si>
     <t>condition1</t>
@@ -63,9 +63,6 @@
     <t>condition2</t>
   </si>
   <si>
-    <t>condition3</t>
-  </si>
-  <si>
     <t>amount_type</t>
   </si>
   <si>
@@ -133,6 +130,12 @@
   </si>
   <si>
     <t>condition_order</t>
+  </si>
+  <si>
+    <t>auto_reward</t>
+  </si>
+  <si>
+    <t>reward_id</t>
   </si>
   <si>
     <t>0并行1顺序</t>
@@ -151,8 +154,8 @@
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -163,22 +166,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -192,8 +218,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -207,24 +241,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,10 +271,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -254,31 +288,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,21 +303,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -321,19 +324,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,37 +468,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -387,19 +480,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,97 +498,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,15 +515,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -554,6 +548,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -573,16 +576,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,11 +609,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,10 +623,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -632,133 +635,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1086,10 +1089,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1111,74 +1114,65 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8">
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1186,25 +1180,22 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1212,25 +1203,22 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1238,25 +1226,22 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1264,25 +1249,22 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>6</v>
       </c>
@@ -1290,25 +1272,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>7</v>
       </c>
@@ -1316,25 +1295,22 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>8</v>
       </c>
@@ -1342,25 +1318,22 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>9</v>
       </c>
@@ -1368,25 +1341,22 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>10</v>
       </c>
@@ -1394,25 +1364,22 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>11</v>
       </c>
@@ -1420,25 +1387,22 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>12</v>
       </c>
@@ -1446,51 +1410,45 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>2</v>
       </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16">
-        <v>13</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
       <c r="G16">
-        <v>2</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>14</v>
       </c>
@@ -1498,25 +1456,22 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17">
-        <v>2</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>15</v>
       </c>
@@ -1524,25 +1479,22 @@
         <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>16</v>
       </c>
@@ -1550,25 +1502,22 @@
         <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>17</v>
       </c>
@@ -1576,25 +1525,22 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>18</v>
       </c>
@@ -1602,25 +1548,22 @@
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>19</v>
       </c>
@@ -1628,25 +1571,22 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>20</v>
       </c>
@@ -1654,25 +1594,22 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>21</v>
       </c>
@@ -1680,25 +1617,22 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1706,25 +1640,22 @@
         <v>4</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>23</v>
       </c>
@@ -1732,25 +1663,22 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>24</v>
       </c>
@@ -1758,25 +1686,22 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>25</v>
       </c>
@@ -1784,25 +1709,22 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>26</v>
       </c>
@@ -1810,25 +1732,22 @@
         <v>7</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>27</v>
       </c>
@@ -1836,21 +1755,18 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30">
         <v>0</v>
       </c>
     </row>
@@ -1863,67 +1779,79 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="2" max="5" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="6:6">
       <c r="F3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1934,16 +1862,22 @@
       <c r="F4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1954,16 +1888,22 @@
       <c r="F5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1974,16 +1914,22 @@
       <c r="F6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1994,16 +1940,22 @@
       <c r="F7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2013,6 +1965,12 @@
       </c>
       <c r="F8">
         <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -10,6 +10,9 @@
     <sheet name="condition" sheetId="1" r:id="rId1"/>
     <sheet name="mission" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">condition!$B:$B</definedName>
+  </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
@@ -49,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -78,7 +81,7 @@
     <t>repeated</t>
   </si>
   <si>
-    <t>1杀怪2对话npc3完成相应条件4使用类型物品5条件池6升级7不是表里的条件8完成相应任务</t>
+    <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
   </si>
   <si>
     <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)</t>
@@ -102,6 +105,9 @@
     <t>[4]</t>
   </si>
   <si>
+    <t>[5]</t>
+  </si>
+  <si>
     <t>[1,2,3,4]</t>
   </si>
   <si>
@@ -145,6 +151,9 @@
   </si>
   <si>
     <t>[1,2,3,4,5,6,7,8,9,10]</t>
+  </si>
+  <si>
+    <t>[1,15,19,22,24,23]</t>
   </si>
 </sst>
 </file>
@@ -152,10 +161,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -163,36 +172,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -210,9 +189,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,22 +205,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,15 +219,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,11 +242,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -287,9 +257,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -304,7 +298,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,37 +333,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -366,37 +477,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,19 +489,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -432,73 +501,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -529,21 +538,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -581,13 +575,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,6 +613,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -623,10 +632,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -635,133 +644,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1341,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>13</v>
@@ -1364,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>13</v>
@@ -1387,7 +1396,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>13</v>
@@ -1410,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>13</v>
@@ -1433,7 +1442,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>13</v>
@@ -1571,7 +1580,7 @@
         <v>3</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>13</v>
@@ -1594,7 +1603,7 @@
         <v>3</v>
       </c>
       <c r="C23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>13</v>
@@ -1617,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>13</v>
@@ -1663,10 +1672,10 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1686,7 +1695,7 @@
         <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>13</v>
@@ -1779,8 +1788,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="2" max="5" width="20.25" customWidth="1"/>
@@ -1791,25 +1800,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1840,7 +1849,7 @@
     </row>
     <row r="3" spans="6:6">
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1848,7 +1857,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -1874,7 +1883,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -1903,7 +1912,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1929,7 +1938,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1955,7 +1964,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1970,6 +1979,32 @@
         <v>1</v>
       </c>
       <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
         <v>1</v>
       </c>
     </row>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16575" windowHeight="10545" activeTab="1"/>
+    <workbookView windowWidth="16575" windowHeight="10545"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -162,9 +162,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -183,7 +183,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -196,18 +217,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -221,24 +235,17 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -298,13 +305,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -333,25 +333,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,151 +495,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,10 +632,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -644,73 +644,73 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -719,58 +719,58 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16575" windowHeight="10545"/>
+    <workbookView windowWidth="16575" windowHeight="10545" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -175,6 +175,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -183,21 +198,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,19 +218,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -244,6 +236,21 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,6 +280,14 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -298,21 +313,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -333,31 +333,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,49 +453,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,7 +489,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,85 +501,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,6 +524,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -538,15 +547,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,23 +569,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,8 +593,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -632,145 +632,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1935,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16575" windowHeight="10545" activeTab="1"/>
+    <workbookView windowWidth="20475" windowHeight="10545" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -144,6 +144,9 @@
     <t>reward_id</t>
   </si>
   <si>
+    <t>next_mission_id</t>
+  </si>
+  <si>
     <t>0并行1顺序</t>
   </si>
   <si>
@@ -154,6 +157,18 @@
   </si>
   <si>
     <t>[1,15,19,22,24,23]</t>
+  </si>
+  <si>
+    <t>[8]</t>
+  </si>
+  <si>
+    <t>[9]</t>
+  </si>
+  <si>
+    <t>[11]</t>
+  </si>
+  <si>
+    <t>[12]</t>
   </si>
 </sst>
 </file>
@@ -161,10 +176,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -172,6 +187,51 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -184,28 +244,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -213,13 +267,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,44 +283,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,7 +306,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,15 +321,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,187 +348,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,78 +539,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -624,6 +567,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -632,10 +647,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -644,133 +659,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1788,14 +1803,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
     <col min="2" max="5" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1820,8 +1835,11 @@
       <c r="H1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1846,13 +1864,16 @@
       <c r="H2" t="s">
         <v>7</v>
       </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="6:6">
       <c r="F3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1877,13 +1898,16 @@
       <c r="H4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -1903,8 +1927,11 @@
       <c r="H5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1912,7 +1939,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1929,8 +1956,11 @@
       <c r="H6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1955,8 +1985,11 @@
       <c r="H7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>5</v>
       </c>
@@ -1964,7 +1997,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1981,13 +2014,16 @@
       <c r="H8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -2006,6 +2042,212 @@
       </c>
       <c r="H9">
         <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -123,6 +123,12 @@
     <t>[10]</t>
   </si>
   <si>
+    <t>[15]</t>
+  </si>
+  <si>
+    <t>[16]</t>
+  </si>
+  <si>
     <t>condition_id</t>
   </si>
   <si>
@@ -169,6 +175,9 @@
   </si>
   <si>
     <t>[12]</t>
+  </si>
+  <si>
+    <t>[27,28]</t>
   </si>
 </sst>
 </file>
@@ -176,10 +185,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -197,24 +206,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -228,38 +229,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,9 +259,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,10 +307,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -313,15 +323,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,6 +336,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -348,25 +357,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -378,31 +489,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,121 +537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,17 +551,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,6 +571,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -579,15 +597,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,7 +620,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,23 +643,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,10 +656,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -659,133 +668,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1113,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1779,7 +1788,7 @@
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
@@ -1791,6 +1800,29 @@
         <v>1</v>
       </c>
       <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
         <v>0</v>
       </c>
     </row>
@@ -1803,7 +1835,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -1815,28 +1847,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1870,7 +1902,7 @@
     </row>
     <row r="3" spans="6:6">
       <c r="F3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1907,7 +1939,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
@@ -1939,7 +1971,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1997,7 +2029,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2023,7 +2055,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -2073,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2102,7 +2134,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2160,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2189,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2232,7 +2264,7 @@
         <v>13</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -2247,6 +2279,93 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
         <v>13</v>
       </c>
     </row>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20475" windowHeight="10545" activeTab="1"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -47,12 +47,24 @@
         </r>
       </text>
     </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>0并行1顺序</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -151,9 +163,6 @@
   </si>
   <si>
     <t>next_mission_id</t>
-  </si>
-  <si>
-    <t>0并行1顺序</t>
   </si>
   <si>
     <t>[1,6,3,8]</t>
@@ -185,10 +194,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -196,36 +205,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -245,7 +224,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -259,14 +266,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -275,10 +274,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -300,6 +300,14 @@
     <font>
       <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -329,15 +337,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -357,43 +366,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,31 +498,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,7 +522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,66 +534,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -520,18 +541,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,26 +557,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -625,6 +614,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -648,6 +646,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -656,145 +665,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1122,7 +1131,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1156,10 +1165,10 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1171,72 +1180,34 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:7">
-      <c r="B3" t="s">
+    <row r="3" spans="3:4">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G4" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>13</v>
@@ -1253,13 +1224,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="s">
-        <v>16</v>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>13</v>
@@ -1276,13 +1247,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
+      <c r="C8" t="s">
+        <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>13</v>
@@ -1291,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1299,13 +1270,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
+      <c r="C9" t="s">
+        <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>13</v>
@@ -1314,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1322,13 +1293,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
-        <v>15</v>
+      <c r="C10" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>13</v>
@@ -1345,13 +1316,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
-        <v>16</v>
+      <c r="C11" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>13</v>
@@ -1368,13 +1339,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
+      <c r="C12" t="s">
+        <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>13</v>
@@ -1391,13 +1362,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>14</v>
+      <c r="C13" t="s">
+        <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>13</v>
@@ -1414,13 +1385,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>13</v>
@@ -1437,13 +1408,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>13</v>
@@ -1460,13 +1431,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>13</v>
@@ -1483,13 +1454,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>13</v>
@@ -1506,22 +1477,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
         <v>2</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1529,22 +1500,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
         <v>2</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -1552,13 +1523,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
-      <c r="C20" t="s">
-        <v>15</v>
+      <c r="C20" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>13</v>
@@ -1575,13 +1546,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
-      <c r="C21" t="s">
-        <v>16</v>
+      <c r="C21" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>13</v>
@@ -1598,13 +1569,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>13</v>
@@ -1621,13 +1592,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>13</v>
@@ -1644,13 +1615,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B24">
         <v>3</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>13</v>
@@ -1667,16 +1638,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1690,16 +1661,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1713,16 +1684,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>14</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1736,16 +1707,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1759,15 +1730,15 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E29">
@@ -1782,13 +1753,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
         <v>13</v>
@@ -1805,24 +1776,70 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
+        <v>26</v>
+      </c>
+      <c r="B31">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>27</v>
+      </c>
+      <c r="B32">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
         <v>28</v>
       </c>
-      <c r="B31">
+      <c r="B33">
         <v>8</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C33" t="s">
         <v>24</v>
       </c>
-      <c r="D31" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31">
+      <c r="D33" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
         <v>0</v>
       </c>
     </row>
@@ -1835,7 +1852,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -1876,10 +1893,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -1897,87 +1914,35 @@
         <v>7</v>
       </c>
       <c r="I2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="6:6">
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>13</v>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1994,10 +1959,10 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2006,13 +1971,13 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -2023,19 +1988,19 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2052,10 +2017,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -2081,13 +2046,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2105,15 +2070,15 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -2134,15 +2099,15 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -2163,15 +2128,15 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -2192,15 +2157,15 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -2221,15 +2186,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
@@ -2250,21 +2215,21 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -2279,21 +2244,21 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -2313,19 +2278,19 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2342,30 +2307,88 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
         <v>16</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19">
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21">
         <v>2</v>
       </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
         <v>13</v>
       </c>
     </row>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="17625" windowHeight="8235"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>repeated</t>
+  </si>
+  <si>
+    <t>server</t>
   </si>
   <si>
     <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
@@ -194,9 +197,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -208,21 +211,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -237,6 +233,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -244,15 +271,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -282,19 +303,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -314,39 +348,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -366,13 +369,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,169 +543,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,16 +563,27 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -586,6 +600,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -608,8 +637,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,37 +652,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -665,10 +668,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -677,133 +680,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1131,7 +1134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1192,48 +1195,45 @@
       <c r="B4" t="s">
         <v>9</v>
       </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
       <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="G4" t="s">
+      <c r="E5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="G5" t="s">
         <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1247,16 +1247,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>16</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1293,22 +1293,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
+      <c r="C10" t="s">
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1316,16 +1316,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1339,16 +1339,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1371,7 +1371,7 @@
         <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1385,16 +1385,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
+      <c r="C14" t="s">
+        <v>17</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1408,16 +1408,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1440,7 +1440,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1454,7 +1454,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1463,7 +1463,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1486,7 +1486,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1500,16 +1500,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1523,22 +1523,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
         <v>2</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -1546,16 +1546,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1569,16 +1569,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1592,7 +1592,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -1601,7 +1601,7 @@
         <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1615,16 +1615,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -1647,7 +1647,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -1670,7 +1670,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1684,15 +1684,15 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E27">
@@ -1707,16 +1707,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1730,16 +1730,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
         <v>22</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1753,16 +1753,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1776,16 +1776,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1799,16 +1799,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33">
         <v>8</v>
@@ -1831,7 +1831,7 @@
         <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1840,6 +1840,29 @@
         <v>1</v>
       </c>
       <c r="G33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>28</v>
+      </c>
+      <c r="B34">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34">
         <v>0</v>
       </c>
     </row>
@@ -1852,7 +1875,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -1864,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1928,73 +1951,44 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>13</v>
-      </c>
-    </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2003,33 +1997,33 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2041,18 +2035,18 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2070,19 +2064,19 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
       <c r="D11">
         <v>1</v>
       </c>
@@ -2099,18 +2093,18 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2128,18 +2122,18 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2162,13 +2156,13 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2186,18 +2180,18 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2215,18 +2209,18 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2249,13 +2243,13 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2273,21 +2267,21 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -2302,21 +2296,21 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2331,24 +2325,24 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2360,24 +2354,24 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21">
         <v>2</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2389,7 +2383,36 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
         <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="44">
   <si>
     <t>id</t>
   </si>
@@ -87,13 +87,19 @@
     <t>operator</t>
   </si>
   <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
     <t>uint32</t>
   </si>
   <si>
     <t>repeated</t>
   </si>
   <si>
-    <t>server</t>
+    <t>common</t>
   </si>
   <si>
     <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
@@ -218,47 +224,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,7 +240,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -304,20 +285,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -329,6 +296,14 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -348,8 +323,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -369,73 +375,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,109 +555,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -560,17 +566,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -604,21 +599,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -630,15 +610,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +631,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -668,10 +674,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -680,133 +686,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1134,10 +1140,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1159,67 +1165,82 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="3:4">
       <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1230,10 +1251,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1253,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1276,10 +1297,10 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1299,10 +1320,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1322,10 +1343,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1345,10 +1366,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1368,10 +1389,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1391,10 +1412,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1414,10 +1435,10 @@
         <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1437,10 +1458,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1460,10 +1481,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1483,10 +1504,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1506,10 +1527,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1529,10 +1550,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1552,10 +1573,10 @@
         <v>2</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1575,10 +1596,10 @@
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1598,10 +1619,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1621,10 +1642,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1644,10 +1665,10 @@
         <v>3</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1667,10 +1688,10 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1690,10 +1711,10 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1713,10 +1734,10 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1736,10 +1757,10 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1759,10 +1780,10 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1782,10 +1803,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1805,10 +1826,10 @@
         <v>7</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1828,10 +1849,10 @@
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1851,10 +1872,10 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1887,68 +1908,68 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1956,10 +1977,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1977,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1985,10 +2006,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2006,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2014,10 +2035,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2035,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2043,10 +2064,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2064,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2072,10 +2093,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2093,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2101,10 +2122,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2122,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2130,10 +2151,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2151,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2159,10 +2180,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2180,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2188,10 +2209,10 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2209,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2217,10 +2238,10 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2238,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2246,10 +2267,10 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2267,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2275,10 +2296,10 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2296,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2304,10 +2325,10 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -2325,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2333,10 +2354,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -2354,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2362,10 +2383,10 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2383,7 +2404,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2391,10 +2412,10 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2412,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17625" windowHeight="8235"/>
+    <workbookView windowWidth="17625" windowHeight="9930"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>common</t>
+  </si>
+  <si>
+    <t>key</t>
   </si>
   <si>
     <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
@@ -203,8 +206,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -217,6 +220,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -224,8 +242,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,30 +273,23 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -292,22 +319,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -325,7 +336,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,22 +344,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -361,6 +357,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -375,55 +378,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,127 +546,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,16 +572,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -595,6 +598,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -632,27 +646,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -674,10 +677,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -686,133 +689,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1140,7 +1143,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1232,52 +1235,34 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:2">
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="2:7">
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
+      <c r="E6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="G6" t="s">
         <v>15</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1291,16 +1276,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1314,7 +1299,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1323,7 +1308,7 @@
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1337,22 +1322,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>15</v>
+      <c r="C11" t="s">
+        <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1360,16 +1345,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1383,16 +1368,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1406,7 +1391,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1415,7 +1400,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1429,16 +1414,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>15</v>
+      <c r="C15" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1452,16 +1437,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1475,7 +1460,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1484,7 +1469,7 @@
         <v>18</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1498,7 +1483,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1507,7 +1492,7 @@
         <v>19</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1521,7 +1506,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1530,7 +1515,7 @@
         <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1544,16 +1529,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1567,22 +1552,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
         <v>2</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -1590,16 +1575,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1613,16 +1598,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1636,7 +1621,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -1645,7 +1630,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1659,16 +1644,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1682,7 +1667,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -1691,7 +1676,7 @@
         <v>22</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1705,7 +1690,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27">
         <v>3</v>
@@ -1714,7 +1699,7 @@
         <v>23</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1728,15 +1713,15 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E28">
@@ -1751,16 +1736,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1774,16 +1759,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
         <v>25</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1797,16 +1782,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1820,16 +1805,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1843,16 +1828,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1866,7 +1851,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34">
         <v>8</v>
@@ -1875,7 +1860,7 @@
         <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1884,6 +1869,29 @@
         <v>1</v>
       </c>
       <c r="G34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>28</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="G35">
         <v>0</v>
       </c>
     </row>
@@ -1908,28 +1916,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1977,10 +1985,10 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1998,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2006,10 +2014,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2027,7 +2035,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2035,10 +2043,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2056,7 +2064,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2064,10 +2072,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2085,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2093,10 +2101,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2114,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2122,10 +2130,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2143,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2151,10 +2159,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2172,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -2180,10 +2188,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2201,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2209,10 +2217,10 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2230,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2238,10 +2246,10 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2259,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -2267,10 +2275,10 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2288,7 +2296,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2296,10 +2304,10 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2317,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2325,10 +2333,10 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -2346,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2354,10 +2362,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -2375,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2383,10 +2391,10 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2404,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2412,10 +2420,10 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2433,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17625" windowHeight="9930"/>
+    <workbookView windowWidth="28125" windowHeight="12540" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -206,8 +206,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -220,11 +220,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -236,7 +258,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,84 +303,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -350,8 +327,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -364,6 +357,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -378,49 +378,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -432,7 +534,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -444,121 +552,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,21 +569,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -604,10 +589,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -624,15 +607,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -661,6 +635,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -669,6 +658,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -677,10 +677,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -689,133 +689,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1980,6 +1980,35 @@
         <v>10</v>
       </c>
     </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+    </row>
     <row r="7" spans="1:9">
       <c r="A7">
         <v>1</v>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540" activeTab="1"/>
+    <workbookView windowWidth="18105" windowHeight="11100" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="45">
   <si>
     <t>id</t>
   </si>
@@ -102,79 +102,79 @@
     <t>common</t>
   </si>
   <si>
+    <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
+  </si>
+  <si>
+    <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)</t>
+  </si>
+  <si>
+    <t>0: == 1:&lt; 2: &lt;= 3: &gt; 3&gt;=</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>[2]</t>
+  </si>
+  <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>[4]</t>
+  </si>
+  <si>
+    <t>[5]</t>
+  </si>
+  <si>
+    <t>[1,2,3,4]</t>
+  </si>
+  <si>
+    <t>[5,6,7,8]</t>
+  </si>
+  <si>
+    <t>[1,2]</t>
+  </si>
+  <si>
+    <t>[1,2,3,4,5,6,7,8]</t>
+  </si>
+  <si>
+    <t>[10]</t>
+  </si>
+  <si>
+    <t>[15]</t>
+  </si>
+  <si>
+    <t>[16]</t>
+  </si>
+  <si>
+    <t>condition_id</t>
+  </si>
+  <si>
+    <t>random_condition_pool</t>
+  </si>
+  <si>
+    <t>mission_type</t>
+  </si>
+  <si>
+    <t>mission_sub_type</t>
+  </si>
+  <si>
+    <t>condition_order</t>
+  </si>
+  <si>
+    <t>auto_reward</t>
+  </si>
+  <si>
+    <t>reward_id</t>
+  </si>
+  <si>
+    <t>next_mission_id</t>
+  </si>
+  <si>
     <t>key</t>
-  </si>
-  <si>
-    <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
-  </si>
-  <si>
-    <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)</t>
-  </si>
-  <si>
-    <t>0: == 1:&lt; 2: &lt;= 3: &gt; 3&gt;=</t>
-  </si>
-  <si>
-    <t>[1]</t>
-  </si>
-  <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>[2]</t>
-  </si>
-  <si>
-    <t>[3]</t>
-  </si>
-  <si>
-    <t>[4]</t>
-  </si>
-  <si>
-    <t>[5]</t>
-  </si>
-  <si>
-    <t>[1,2,3,4]</t>
-  </si>
-  <si>
-    <t>[5,6,7,8]</t>
-  </si>
-  <si>
-    <t>[1,2]</t>
-  </si>
-  <si>
-    <t>[1,2,3,4,5,6,7,8]</t>
-  </si>
-  <si>
-    <t>[10]</t>
-  </si>
-  <si>
-    <t>[15]</t>
-  </si>
-  <si>
-    <t>[16]</t>
-  </si>
-  <si>
-    <t>condition_id</t>
-  </si>
-  <si>
-    <t>random_condition_pool</t>
-  </si>
-  <si>
-    <t>mission_type</t>
-  </si>
-  <si>
-    <t>mission_sub_type</t>
-  </si>
-  <si>
-    <t>condition_order</t>
-  </si>
-  <si>
-    <t>auto_reward</t>
-  </si>
-  <si>
-    <t>reward_id</t>
-  </si>
-  <si>
-    <t>next_mission_id</t>
   </si>
   <si>
     <t>[1,6,3,8]</t>
@@ -206,8 +206,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -221,32 +221,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -257,8 +241,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,26 +295,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -312,24 +328,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,13 +358,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -378,187 +378,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,6 +569,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -587,35 +602,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,17 +632,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -677,10 +677,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -689,133 +689,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1235,20 +1235,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-    </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1259,10 +1254,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1282,10 +1277,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1305,10 +1300,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1328,10 +1323,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1351,10 +1346,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1374,10 +1369,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1397,10 +1392,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1420,10 +1415,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1443,10 +1438,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1466,10 +1461,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1489,10 +1484,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1512,10 +1507,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1535,10 +1530,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1558,10 +1553,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1581,10 +1576,10 @@
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1604,10 +1599,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1627,10 +1622,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1650,10 +1645,10 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1673,10 +1668,10 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1696,10 +1691,10 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1719,10 +1714,10 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1742,10 +1737,10 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1765,10 +1760,10 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1788,10 +1783,10 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1811,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1834,10 +1829,10 @@
         <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1857,10 +1852,10 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1880,10 +1875,10 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1916,28 +1911,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>32</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>33</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>34</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>35</v>
-      </c>
-      <c r="I1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2009,15 +2004,23 @@
         <v>11</v>
       </c>
     </row>
+    <row r="5" spans="4:5">
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+    </row>
     <row r="7" spans="1:9">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2035,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2046,7 +2049,7 @@
         <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2064,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2072,7 +2075,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>38</v>
@@ -2093,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2101,10 +2104,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2122,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2130,7 +2133,7 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
@@ -2151,7 +2154,7 @@
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2162,7 +2165,7 @@
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2180,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2188,10 +2191,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2217,10 +2220,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2246,10 +2249,10 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2267,7 +2270,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2275,10 +2278,10 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2304,10 +2307,10 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2333,10 +2336,10 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2354,7 +2357,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -2362,10 +2365,10 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19">
         <v>9</v>
@@ -2383,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -2394,7 +2397,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -2412,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -2420,10 +2423,10 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2441,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -2449,10 +2452,10 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -2470,7 +2473,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -206,10 +206,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -220,44 +220,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,9 +243,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,11 +295,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -303,27 +318,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -342,13 +340,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,8 +348,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -378,187 +378,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,17 +572,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -602,50 +596,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -669,6 +630,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -677,10 +677,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -689,133 +689,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1899,7 +1899,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -2012,41 +2012,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
-      </c>
-    </row>
     <row r="8" spans="1:9">
       <c r="A8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -2055,13 +2026,13 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2072,13 +2043,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2087,10 +2058,10 @@
         <v>2</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -2101,19 +2072,19 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2130,13 +2101,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2159,13 +2130,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2188,10 +2159,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -2212,12 +2183,12 @@
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -2241,15 +2212,15 @@
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -2270,15 +2241,15 @@
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -2299,15 +2270,15 @@
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -2328,15 +2299,15 @@
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
         <v>16</v>
@@ -2357,21 +2328,21 @@
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
       </c>
       <c r="D19">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -2391,16 +2362,16 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -2420,19 +2391,19 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
         <v>16</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21">
         <v>0</v>
@@ -2449,7 +2420,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
@@ -2461,7 +2432,7 @@
         <v>2</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2473,6 +2444,35 @@
         <v>1</v>
       </c>
       <c r="I22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
         <v>16</v>
       </c>
     </row>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18105" windowHeight="11100" activeTab="1"/>
+    <workbookView windowWidth="18105" windowHeight="11100"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
-    <sheet name="mission" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">condition!$B:$B</definedName>
@@ -17,54 +16,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>luhailong</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1:主线</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1:主线1</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0并行1顺序</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -148,57 +101,6 @@
   </si>
   <si>
     <t>[16]</t>
-  </si>
-  <si>
-    <t>condition_id</t>
-  </si>
-  <si>
-    <t>random_condition_pool</t>
-  </si>
-  <si>
-    <t>mission_type</t>
-  </si>
-  <si>
-    <t>mission_sub_type</t>
-  </si>
-  <si>
-    <t>condition_order</t>
-  </si>
-  <si>
-    <t>auto_reward</t>
-  </si>
-  <si>
-    <t>reward_id</t>
-  </si>
-  <si>
-    <t>next_mission_id</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>[1,6,3,8]</t>
-  </si>
-  <si>
-    <t>[1,2,3,4,5,6,7,8,9,10]</t>
-  </si>
-  <si>
-    <t>[1,15,19,22,24,23]</t>
-  </si>
-  <si>
-    <t>[8]</t>
-  </si>
-  <si>
-    <t>[9]</t>
-  </si>
-  <si>
-    <t>[11]</t>
-  </si>
-  <si>
-    <t>[12]</t>
-  </si>
-  <si>
-    <t>[27,28]</t>
   </si>
 </sst>
 </file>
@@ -206,17 +108,107 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -229,90 +221,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,8 +242,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -350,23 +260,10 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -378,187 +275,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,15 +466,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -614,19 +502,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -655,6 +541,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -677,10 +574,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -689,133 +586,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1894,591 +1791,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="13.875" customWidth="1"/>
-    <col min="2" max="5" width="20.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="2:9">
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="4:5">
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16">
-        <v>9</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17">
-        <v>10</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
-      </c>
-      <c r="I17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20">
-        <v>13</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20">
-        <v>9</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23">
-        <v>16</v>
-      </c>
-      <c r="B23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23">
-        <v>0</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
-      </c>
-      <c r="I23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -110,8 +110,8 @@
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -123,9 +123,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -136,22 +151,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -165,8 +167,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -182,7 +222,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -196,11 +251,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -211,60 +265,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -275,13 +275,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,25 +431,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,102 +449,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -432,30 +456,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,6 +466,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -480,6 +489,47 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -502,15 +552,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -525,47 +566,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -574,10 +574,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -586,133 +586,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\turn-based-game\bin\config\xlsx\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD32BB9-A23F-477D-ADD9-90E5438055E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18105" windowHeight="11100"/>
+    <workbookView xWindow="9375" yWindow="4230" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -37,9 +43,6 @@
     <t>amount</t>
   </si>
   <si>
-    <t>operator</t>
-  </si>
-  <si>
     <t>design</t>
   </si>
   <si>
@@ -61,9 +64,6 @@
     <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)</t>
   </si>
   <si>
-    <t>0: == 1:&lt; 2: &lt;= 3: &gt; 3&gt;=</t>
-  </si>
-  <si>
     <t>[1]</t>
   </si>
   <si>
@@ -101,19 +101,21 @@
   </si>
   <si>
     <t>[16]</t>
+  </si>
+  <si>
+    <t>operation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">0: &gt;= 1:&gt; 2: &lt;= 3: &lt; 4:== </t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="20">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,345 +124,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -468,315 +155,32 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1034,16 +438,16 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1062,122 +466,122 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="3:4">
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1189,7 +593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>3</v>
       </c>
@@ -1197,10 +601,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1212,7 +616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1220,10 +624,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1235,7 +639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1243,10 +647,10 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1258,7 +662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>6</v>
       </c>
@@ -1266,10 +670,10 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1281,7 +685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>7</v>
       </c>
@@ -1289,10 +693,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1304,7 +708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>8</v>
       </c>
@@ -1312,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1327,7 +731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>9</v>
       </c>
@@ -1335,10 +739,10 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1350,7 +754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>10</v>
       </c>
@@ -1358,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1373,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>11</v>
       </c>
@@ -1381,10 +785,10 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1396,7 +800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>12</v>
       </c>
@@ -1404,10 +808,10 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1419,7 +823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>13</v>
       </c>
@@ -1427,10 +831,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1442,7 +846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>14</v>
       </c>
@@ -1450,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1465,7 +869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>15</v>
       </c>
@@ -1473,10 +877,10 @@
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1488,7 +892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>16</v>
       </c>
@@ -1496,10 +900,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1511,7 +915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>17</v>
       </c>
@@ -1519,10 +923,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1534,7 +938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>18</v>
       </c>
@@ -1542,10 +946,10 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1557,7 +961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>19</v>
       </c>
@@ -1565,10 +969,10 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1580,7 +984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>20</v>
       </c>
@@ -1588,10 +992,10 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1603,7 +1007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>21</v>
       </c>
@@ -1611,10 +1015,10 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1626,7 +1030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>22</v>
       </c>
@@ -1634,11 +1038,11 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
         <v>15</v>
       </c>
-      <c r="D29" t="s">
-        <v>17</v>
-      </c>
       <c r="E29">
         <v>0</v>
       </c>
@@ -1649,7 +1053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>23</v>
       </c>
@@ -1657,10 +1061,10 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1672,7 +1076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>24</v>
       </c>
@@ -1680,10 +1084,10 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1695,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>25</v>
       </c>
@@ -1703,10 +1107,10 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1718,7 +1122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>26</v>
       </c>
@@ -1726,10 +1130,10 @@
         <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1741,7 +1145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>27</v>
       </c>
@@ -1749,10 +1153,10 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1764,7 +1168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>28</v>
       </c>
@@ -1772,10 +1176,10 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1788,7 +1192,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\turn-based-game\bin\config\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD32BB9-A23F-477D-ADD9-90E5438055E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12445EE-B33A-4F00-B1C4-35EE04A8B77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9375" yWindow="4230" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8145" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -108,6 +108,14 @@
   </si>
   <si>
     <t xml:space="preserve">0: &gt;= 1:&gt; 2: &lt;= 3: &lt; 4:== </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>condition3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>condition4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -444,10 +452,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -460,23 +468,29 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -498,16 +512,28 @@
       <c r="G2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -530,24 +556,30 @@
         <v>10</v>
       </c>
       <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>1</v>
       </c>
@@ -560,17 +592,23 @@
       <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
+      <c r="E8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>2</v>
       </c>
@@ -583,17 +621,23 @@
       <c r="D9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
+      <c r="E9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>3</v>
       </c>
@@ -606,17 +650,23 @@
       <c r="D10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
+      <c r="E10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>4</v>
       </c>
@@ -629,17 +679,23 @@
       <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>5</v>
       </c>
@@ -652,17 +708,23 @@
       <c r="D12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
+      <c r="E12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>6</v>
       </c>
@@ -675,17 +737,23 @@
       <c r="D13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
+      <c r="E13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>7</v>
       </c>
@@ -698,17 +766,23 @@
       <c r="D14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
+      <c r="E14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>8</v>
       </c>
@@ -721,17 +795,23 @@
       <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
+      <c r="E15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>9</v>
       </c>
@@ -744,17 +824,23 @@
       <c r="D16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
+      <c r="E16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>10</v>
       </c>
@@ -767,17 +853,23 @@
       <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>2</v>
+      <c r="E17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>11</v>
       </c>
@@ -790,17 +882,23 @@
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
+      <c r="E18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H18">
+        <v>2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>12</v>
       </c>
@@ -813,17 +911,23 @@
       <c r="D19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
+      <c r="E19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>13</v>
       </c>
@@ -836,17 +940,23 @@
       <c r="D20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H20">
+        <v>2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>14</v>
       </c>
@@ -859,17 +969,23 @@
       <c r="D21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>2</v>
+      <c r="E21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>15</v>
       </c>
@@ -882,17 +998,23 @@
       <c r="D22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
+      <c r="E22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>16</v>
       </c>
@@ -905,17 +1027,23 @@
       <c r="D23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
+      <c r="E23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>17</v>
       </c>
@@ -928,17 +1056,23 @@
       <c r="D24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
+      <c r="E24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>18</v>
       </c>
@@ -951,17 +1085,23 @@
       <c r="D25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
+      <c r="E25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>19</v>
       </c>
@@ -974,17 +1114,23 @@
       <c r="D26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
+      <c r="E26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>20</v>
       </c>
@@ -997,17 +1143,23 @@
       <c r="D27" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
+      <c r="E27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>21</v>
       </c>
@@ -1020,17 +1172,23 @@
       <c r="D28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
+      <c r="E28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>22</v>
       </c>
@@ -1043,17 +1201,23 @@
       <c r="D29" t="s">
         <v>15</v>
       </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
+      <c r="E29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>23</v>
       </c>
@@ -1066,17 +1230,23 @@
       <c r="D30" t="s">
         <v>22</v>
       </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
+      <c r="E30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>24</v>
       </c>
@@ -1089,17 +1259,23 @@
       <c r="D31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
+      <c r="E31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>25</v>
       </c>
@@ -1112,17 +1288,23 @@
       <c r="D32" t="s">
         <v>14</v>
       </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
+      <c r="E32" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>26</v>
       </c>
@@ -1135,17 +1317,23 @@
       <c r="D33" t="s">
         <v>14</v>
       </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>27</v>
       </c>
@@ -1158,17 +1346,23 @@
       <c r="D34" t="s">
         <v>14</v>
       </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>28</v>
       </c>
@@ -1181,19 +1375,25 @@
       <c r="D35" t="s">
         <v>14</v>
       </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
+      <c r="E35" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
       </c>
       <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\turn-based-game\bin\config\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\turn-based-game\bin\config\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12445EE-B33A-4F00-B1C4-35EE04A8B77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8145" yWindow="3465" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8145" yWindow="3465" windowWidth="21600" windowHeight="11295"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -58,9 +57,6 @@
     <t>common</t>
   </si>
   <si>
-    <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
-  </si>
-  <si>
     <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)</t>
   </si>
   <si>
@@ -116,13 +112,17 @@
   </si>
   <si>
     <t>condition4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -451,7 +451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
@@ -469,10 +469,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -481,7 +481,7 @@
         <v>5</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J1" t="s">
         <v>6</v>
@@ -570,13 +570,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
         <v>11</v>
       </c>
-      <c r="G6" t="s">
-        <v>12</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.15">
@@ -587,16 +587,16 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -616,16 +616,16 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -645,16 +645,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -674,16 +674,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -703,16 +703,16 @@
         <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -732,16 +732,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -761,16 +761,16 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -790,16 +790,16 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -819,16 +819,16 @@
         <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -848,16 +848,16 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -877,16 +877,16 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -906,16 +906,16 @@
         <v>1</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -935,16 +935,16 @@
         <v>1</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -964,16 +964,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -993,16 +993,16 @@
         <v>2</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1022,16 +1022,16 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1051,16 +1051,16 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1080,16 +1080,16 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1109,16 +1109,16 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1138,16 +1138,16 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1167,16 +1167,16 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1196,16 +1196,16 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1225,16 +1225,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1254,16 +1254,16 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1283,16 +1283,16 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1312,16 +1312,16 @@
         <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1341,16 +1341,16 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1370,16 +1370,16 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35">
         <v>0</v>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\github\turn-based-game\bin\config\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="8145" yWindow="3465" windowWidth="21600" windowHeight="11295"/>
+    <workbookView windowWidth="21360" windowHeight="10620"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -22,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -36,12 +31,21 @@
     <t>condition2</t>
   </si>
   <si>
+    <t>condition3</t>
+  </si>
+  <si>
+    <t>condition4</t>
+  </si>
+  <si>
     <t>amount_type</t>
   </si>
   <si>
     <t>amount</t>
   </si>
   <si>
+    <t>operation</t>
+  </si>
+  <si>
     <t>design</t>
   </si>
   <si>
@@ -57,9 +61,18 @@
     <t>common</t>
   </si>
   <si>
+    <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
+  </si>
+  <si>
     <t>0:累计 (如累计充值人民币1万元) 1:拥有 (如拥有一万砖石)</t>
   </si>
   <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0: &gt;= 1:&gt; 2: &lt;= 3: &lt; 4:== </t>
+  </si>
+  <si>
     <t>[1]</t>
   </si>
   <si>
@@ -99,31 +112,20 @@
     <t>[16]</t>
   </si>
   <si>
-    <t>operation</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">0: &gt;= 1:&gt; 2: &lt;= 3: &lt; 4:== </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>condition3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>condition4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1杀怪2对话npc3完成相应条件4使用类型物品5交互6升级7不是表里的条件8完成相应任务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>杀春节的年兽2个</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,9 +134,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -142,20 +144,342 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -163,9 +487,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -173,22 +739,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
+    <cellStyle name="输入" xfId="3" builtinId="20"/>
+    <cellStyle name="货币" xfId="4" builtinId="4"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
+    <cellStyle name="差" xfId="7" builtinId="27"/>
+    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
+    <cellStyle name="超链接" xfId="10" builtinId="8"/>
+    <cellStyle name="百分比" xfId="11" builtinId="5"/>
+    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
+    <cellStyle name="注释" xfId="13" builtinId="10"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
+    <cellStyle name="标题" xfId="17" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
+    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="计算" xfId="25" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
+    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
+    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
+    <cellStyle name="汇总" xfId="30" builtinId="25"/>
+    <cellStyle name="好" xfId="31" builtinId="26"/>
+    <cellStyle name="适中" xfId="32" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
+    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
+    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
+    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
+    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -446,16 +1056,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="10" max="10" width="13.625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -468,135 +1081,138 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>28</v>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>25</v>
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="3:6">
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+      <c r="K4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    </row>
+    <row r="6" spans="2:9">
       <c r="B6" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>13</v>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -608,24 +1224,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>13</v>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -637,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>3</v>
       </c>
@@ -645,16 +1261,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -666,7 +1282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>4</v>
       </c>
@@ -674,16 +1290,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -695,24 +1311,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -724,24 +1340,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>6</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>13</v>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -753,7 +1369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>7</v>
       </c>
@@ -761,16 +1377,16 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -782,7 +1398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>8</v>
       </c>
@@ -790,16 +1406,16 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -811,24 +1427,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>9</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>13</v>
+      <c r="C16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -840,24 +1456,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>10</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>13</v>
+      <c r="C17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -869,24 +1485,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>11</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>13</v>
+      <c r="C18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -898,24 +1514,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>12</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>13</v>
+      <c r="C19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -927,24 +1543,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>13</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>13</v>
+      <c r="C20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -956,24 +1572,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>14</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>13</v>
+      <c r="C21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -985,24 +1601,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>15</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>13</v>
+      <c r="C22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -1014,24 +1630,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>16</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>13</v>
+      <c r="C23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -1043,7 +1659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>17</v>
       </c>
@@ -1051,16 +1667,16 @@
         <v>2</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -1072,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>18</v>
       </c>
@@ -1080,16 +1696,16 @@
         <v>2</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -1101,7 +1717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>19</v>
       </c>
@@ -1109,16 +1725,16 @@
         <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -1130,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>20</v>
       </c>
@@ -1138,16 +1754,16 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1159,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>21</v>
       </c>
@@ -1167,16 +1783,16 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -1188,7 +1804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>22</v>
       </c>
@@ -1196,16 +1812,16 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -1217,7 +1833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>23</v>
       </c>
@@ -1225,16 +1841,16 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -1246,7 +1862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>24</v>
       </c>
@@ -1254,16 +1870,16 @@
         <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -1275,7 +1891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>25</v>
       </c>
@@ -1283,16 +1899,16 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1304,7 +1920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:9">
       <c r="A33">
         <v>26</v>
       </c>
@@ -1312,16 +1928,16 @@
         <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -1333,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:9">
       <c r="A34">
         <v>27</v>
       </c>
@@ -1341,16 +1957,16 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -1362,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:9">
       <c r="A35">
         <v>28</v>
       </c>
@@ -1370,16 +1986,16 @@
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1391,9 +2007,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="36" spans="1:10">
+      <c r="A36">
+        <v>29</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21360" windowHeight="10620"/>
+    <workbookView windowWidth="21220" windowHeight="17160"/>
   </bookViews>
   <sheets>
     <sheet name="condition" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">condition!$B:$B</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -43,7 +56,7 @@
     <t>amount</t>
   </si>
   <si>
-    <t>operation</t>
+    <t>comparison</t>
   </si>
   <si>
     <t>design</t>
@@ -118,54 +131,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -182,14 +160,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -229,6 +199,21 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -279,7 +264,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,49 +300,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -348,121 +438,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,21 +491,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -532,6 +523,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,148 +596,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -739,59 +745,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1063,9 +1069,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="10" max="10" width="13.625" customWidth="1"/>
+    <col min="10" max="10" width="13.6272727272727" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21220" windowHeight="17160"/>
+    <workbookView windowWidth="21440" windowHeight="8760"/>
   </bookViews>
   <sheets>
-    <sheet name="condition" sheetId="1" r:id="rId1"/>
+    <sheet name="Condition" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">condition!$B:$B</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Condition!$B:$B</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>

--- a/bin/config/xlsx/conditions.xlsx
+++ b/bin/config/xlsx/conditions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21440" windowHeight="8760"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Condition" sheetId="1" r:id="rId1"/>
@@ -818,7 +818,7 @@
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window" lastClr="CCE8CF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1068,10 +1068,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:K38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="10" max="10" width="13.6272727272727" customWidth="1"/>
+    <col min="10" max="10" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1201,73 +1201,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-    </row>
     <row r="10" spans="1:9">
       <c r="A10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
+      <c r="C10" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
@@ -1290,13 +1232,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11">
         <v>1</v>
       </c>
-      <c r="C11" t="s">
-        <v>22</v>
+      <c r="C11" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>19</v>
@@ -1319,13 +1261,13 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>18</v>
+      <c r="C12" t="s">
+        <v>21</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>19</v>
@@ -1340,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1348,13 +1290,13 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>20</v>
+      <c r="C13" t="s">
+        <v>22</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>19</v>
@@ -1369,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1377,13 +1319,13 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
-      <c r="C14" t="s">
-        <v>21</v>
+      <c r="C14" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>19</v>
@@ -1406,13 +1348,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
-      <c r="C15" t="s">
-        <v>22</v>
+      <c r="C15" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>19</v>
@@ -1435,13 +1377,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>18</v>
+      <c r="C16" t="s">
+        <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>19</v>
@@ -1464,13 +1406,13 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>20</v>
+      <c r="C17" t="s">
+        <v>22</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>19</v>
@@ -1493,13 +1435,13 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>19</v>
@@ -1522,13 +1464,13 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>19</v>
@@ -1551,13 +1493,13 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>19</v>
@@ -1580,13 +1522,13 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>19</v>
@@ -1609,28 +1551,28 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
         <v>2</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1638,28 +1580,28 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
         <v>2</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1667,13 +1609,13 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24" t="s">
-        <v>21</v>
+      <c r="C24" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>19</v>
@@ -1696,13 +1638,13 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
-      <c r="C25" t="s">
-        <v>22</v>
+      <c r="C25" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>19</v>
@@ -1725,13 +1667,13 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>19</v>
@@ -1754,13 +1696,13 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>19</v>
@@ -1783,13 +1725,13 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>19</v>
@@ -1812,16 +1754,16 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>19</v>
@@ -1841,16 +1783,16 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>19</v>
@@ -1870,16 +1812,16 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>19</v>
@@ -1899,21 +1841,21 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-      <c r="F32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G32">
@@ -1928,21 +1870,21 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G33">
@@ -1957,13 +1899,13 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
         <v>19</v>
@@ -1986,62 +1928,120 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35">
+        <v>26</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36">
+        <v>27</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s">
+        <v>19</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37">
         <v>28</v>
       </c>
-      <c r="B35">
+      <c r="B37">
         <v>8</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C37" t="s">
         <v>30</v>
       </c>
-      <c r="D35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36">
+      <c r="D37" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38">
         <v>29</v>
       </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
         <v>18</v>
       </c>
-      <c r="D36" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
+      <c r="D38" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" t="s">
+        <v>19</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
         <v>2</v>
       </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36" t="s">
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38" t="s">
         <v>31</v>
       </c>
     </row>
